--- a/6.4 Bonaire with disturbances/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/6.4 Bonaire with disturbances/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -777,10 +777,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11.39121861237574</v>
+        <v>9.718320524339175</v>
       </c>
       <c r="D2" t="n">
-        <v>98.74516584084844</v>
+        <v>105.8294572746934</v>
       </c>
     </row>
     <row r="3">
@@ -788,13 +788,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.492256510455152</v>
+        <v>1.826050729899067</v>
       </c>
       <c r="C3" t="n">
-        <v>14.94220005863645</v>
+        <v>14.88820393490288</v>
       </c>
       <c r="D3" t="n">
-        <v>310.2960881427682</v>
+        <v>306.6979828067036</v>
       </c>
     </row>
     <row r="4">
@@ -802,13 +802,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.70792221021996</v>
+        <v>12.07353326682727</v>
       </c>
       <c r="C4" t="n">
-        <v>68.791061636574</v>
+        <v>63.35414285045516</v>
       </c>
       <c r="D4" t="n">
-        <v>291.7174945876014</v>
+        <v>292.7512749201734</v>
       </c>
     </row>
     <row r="5">
@@ -816,13 +816,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.03961406553514</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="C5" t="n">
-        <v>96.67760517570468</v>
+        <v>81.60777791551612</v>
       </c>
       <c r="D5" t="n">
-        <v>162.6510509010903</v>
+        <v>170.0632460681537</v>
       </c>
     </row>
     <row r="6">
@@ -830,13 +830,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>9.096874227550947</v>
       </c>
       <c r="C6" t="n">
-        <v>51.07935130425731</v>
+        <v>39.04410619789565</v>
       </c>
       <c r="D6" t="n">
-        <v>115.441749046974</v>
+        <v>118.9436431080223</v>
       </c>
     </row>
     <row r="7">
@@ -844,13 +844,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>3.952516257297658</v>
+        <v>3.473423377625215</v>
       </c>
       <c r="C7" t="n">
-        <v>12.99539436111503</v>
+        <v>10.54004335279375</v>
       </c>
       <c r="D7" t="n">
-        <v>106.6580523370777</v>
+        <v>102.9450825196163</v>
       </c>
     </row>
     <row r="8">
@@ -858,13 +858,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.00414797499524</v>
+        <v>2.837250865273282</v>
       </c>
       <c r="C8" t="n">
-        <v>7.42692138262712</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="D8" t="n">
-        <v>137.7735640754761</v>
+        <v>120.3328161095315</v>
       </c>
     </row>
     <row r="9">
@@ -872,13 +872,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="D9" t="n">
-        <v>151.0968621698096</v>
+        <v>140.4468630741401</v>
       </c>
     </row>
     <row r="10">
@@ -886,13 +886,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="D10" t="n">
-        <v>160.147594255261</v>
+        <v>158.8664135012189</v>
       </c>
     </row>
     <row r="11">
@@ -900,13 +900,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.132356013624072</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>9.595602061308321</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="D11" t="n">
-        <v>168.9892140797077</v>
+        <v>170.9438737588631</v>
       </c>
     </row>
     <row r="12">
@@ -914,13 +914,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>7.593818492349078</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="D12" t="n">
-        <v>165.7622093758484</v>
+        <v>182.4686100590164</v>
       </c>
     </row>
     <row r="13">
@@ -928,13 +928,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>7.284567965511334</v>
+        <v>6.50407854063512</v>
       </c>
       <c r="D13" t="n">
-        <v>124.8783079801943</v>
+        <v>168.5857157732623</v>
       </c>
     </row>
     <row r="14">
@@ -942,13 +942,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>9.833185005736054</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>103.8630166230871</v>
+        <v>138.5864511745925</v>
       </c>
     </row>
     <row r="15">
@@ -956,13 +956,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.150027472300515</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>75.6092994425681</v>
+        <v>123.2682417452295</v>
       </c>
     </row>
     <row r="16">
@@ -970,13 +970,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>109.5286826242954</v>
       </c>
     </row>
     <row r="17">
@@ -984,13 +984,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>83.11083365071798</v>
       </c>
     </row>
     <row r="18">
@@ -998,13 +998,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C18" t="n">
-        <v>4.280419990516093</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="19">
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -1088,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>15.78748483199296</v>
+        <v>13.34980528234813</v>
       </c>
       <c r="D2" t="n">
-        <v>87.717193879044</v>
+        <v>94.43332992379645</v>
       </c>
     </row>
     <row r="3">
@@ -1099,13 +1099,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5939573610693203</v>
+        <v>0.7608544707912781</v>
       </c>
       <c r="C3" t="n">
-        <v>31.34229545807942</v>
+        <v>27.21404636172158</v>
       </c>
       <c r="D3" t="n">
-        <v>311.4741853878643</v>
+        <v>312.4706593076749</v>
       </c>
     </row>
     <row r="4">
@@ -1113,13 +1113,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6.304783756673016</v>
+        <v>7.40237769002095</v>
       </c>
       <c r="C4" t="n">
-        <v>51.45928766580082</v>
+        <v>49.96604940764141</v>
       </c>
       <c r="D4" t="n">
-        <v>354.8674339155733</v>
+        <v>351.6767538767712</v>
       </c>
     </row>
     <row r="5">
@@ -1127,13 +1127,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.59782759862408</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>113.3673161479005</v>
+        <v>98.81290643244149</v>
       </c>
       <c r="D5" t="n">
-        <v>203.5899301681823</v>
+        <v>212.2783973507666</v>
       </c>
     </row>
     <row r="6">
@@ -1141,13 +1141,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.11324514335366</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>101.1121595557875</v>
+        <v>81.79136473621028</v>
       </c>
       <c r="D6" t="n">
-        <v>131.0996431820063</v>
+        <v>137.3789014983689</v>
       </c>
     </row>
     <row r="7">
@@ -1155,13 +1155,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>42.10028680121597</v>
+        <v>31.02126395879071</v>
       </c>
       <c r="D7" t="n">
-        <v>112.347280283188</v>
+        <v>110.5506819844163</v>
       </c>
     </row>
     <row r="8">
@@ -1169,13 +1169,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="C8" t="n">
-        <v>12.10004045484194</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="D8" t="n">
-        <v>138.4411525143639</v>
+        <v>121.5845444324462</v>
       </c>
     </row>
     <row r="9">
@@ -1183,13 +1183,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.328124717396686</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="D9" t="n">
-        <v>153.9812369248867</v>
+        <v>139.4484256589212</v>
       </c>
     </row>
     <row r="10">
@@ -1197,13 +1197,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>9.537678946757763</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="D10" t="n">
-        <v>163.2793694318083</v>
+        <v>159.2934737525662</v>
       </c>
     </row>
     <row r="11">
@@ -1211,13 +1211,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.132356013624072</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>10.30638739918301</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="D11" t="n">
-        <v>168.811517745239</v>
+        <v>171.4769627622691</v>
       </c>
     </row>
     <row r="12">
@@ -1225,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>8.895615948180348</v>
+        <v>8.027750977626168</v>
       </c>
       <c r="D12" t="n">
-        <v>163.3755807068245</v>
+        <v>182.4686100590164</v>
       </c>
     </row>
     <row r="13">
@@ -1239,13 +1239,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>7.804894248762142</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="D13" t="n">
-        <v>121.496187139064</v>
+        <v>170.1466946230147</v>
       </c>
     </row>
     <row r="14">
@@ -1253,13 +1253,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>9.833185005736054</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>99.56099818307754</v>
+        <v>140.430173363168</v>
       </c>
     </row>
     <row r="15">
@@ -1267,13 +1267,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.791689560250429</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>69.15921702566655</v>
+        <v>123.6265796572796</v>
       </c>
     </row>
     <row r="16">
@@ -1281,13 +1281,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>34.30521002949629</v>
+        <v>109.5286826242954</v>
       </c>
     </row>
     <row r="17">
@@ -1295,13 +1295,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="D17" t="n">
-        <v>8.9721922691116</v>
+        <v>83.11083365071798</v>
       </c>
     </row>
     <row r="18">
@@ -1309,13 +1309,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>4.280419990516093</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="19">
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -1399,10 +1399,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12.21981367476005</v>
+        <v>10.45364955482004</v>
       </c>
       <c r="D2" t="n">
-        <v>155.2447462202524</v>
+        <v>169.7834479724434</v>
       </c>
     </row>
     <row r="3">
@@ -1410,13 +1410,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2503456645829367</v>
+        <v>0.3288854809226815</v>
       </c>
       <c r="C3" t="n">
-        <v>47.58040248632167</v>
+        <v>39.48589266480671</v>
       </c>
       <c r="D3" t="n">
-        <v>309.2603443147877</v>
+        <v>310.0801036478338</v>
       </c>
     </row>
     <row r="4">
@@ -1424,13 +1424,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.445934441906304</v>
+        <v>4.160646770597982</v>
       </c>
       <c r="C4" t="n">
-        <v>65.08987279156354</v>
+        <v>58.69574999380406</v>
       </c>
       <c r="D4" t="n">
-        <v>400.8515146347897</v>
+        <v>395.1082905649458</v>
       </c>
     </row>
     <row r="5">
@@ -1438,13 +1438,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.89173001509237</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="C5" t="n">
-        <v>104.212518805799</v>
+        <v>95.52405162321466</v>
       </c>
       <c r="D5" t="n">
-        <v>254.5180923259856</v>
+        <v>263.7219770532995</v>
       </c>
     </row>
     <row r="6">
@@ -1452,13 +1452,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.69564251615027</v>
+        <v>21.37362926915731</v>
       </c>
       <c r="C6" t="n">
-        <v>138.3851928952219</v>
+        <v>115.6832589822187</v>
       </c>
       <c r="D6" t="n">
-        <v>148.9311267342412</v>
+        <v>158.5512724881557</v>
       </c>
     </row>
     <row r="7">
@@ -1466,13 +1466,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="C7" t="n">
-        <v>89.82991493858314</v>
+        <v>69.46846755250429</v>
       </c>
       <c r="D7" t="n">
-        <v>119.5935600882337</v>
+        <v>120.4319726276605</v>
       </c>
     </row>
     <row r="8">
@@ -1480,13 +1480,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>139.6094322824177</v>
+        <v>123.8376554136927</v>
       </c>
     </row>
     <row r="9">
@@ -1494,13 +1494,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.660937189136355</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>11.75937400146829</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="D9" t="n">
-        <v>156.8656116799638</v>
+        <v>138.7828007154418</v>
       </c>
     </row>
     <row r="10">
@@ -1508,13 +1508,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>10.2494460323367</v>
+        <v>9.252972112526189</v>
       </c>
       <c r="D10" t="n">
-        <v>166.4111446083556</v>
+        <v>159.5781805867978</v>
       </c>
     </row>
     <row r="11">
@@ -1522,13 +1522,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.310052348092745</v>
+        <v>2.132356013624072</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83947640258903</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="D11" t="n">
-        <v>168.6338214107703</v>
+        <v>172.0100517656751</v>
       </c>
     </row>
     <row r="12">
@@ -1536,13 +1536,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>9.980447161373073</v>
+        <v>8.895615948180348</v>
       </c>
       <c r="D12" t="n">
-        <v>159.9041208246077</v>
+        <v>180.7328801179081</v>
       </c>
     </row>
     <row r="13">
@@ -1550,13 +1550,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>8.585383673638358</v>
+        <v>7.544731107136739</v>
       </c>
       <c r="D13" t="n">
-        <v>118.3742294395592</v>
+        <v>171.9678366143926</v>
       </c>
     </row>
     <row r="14">
@@ -1564,13 +1564,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>9.833185005736054</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>95.25897974306801</v>
+        <v>142.888469614602</v>
       </c>
     </row>
     <row r="15">
@@ -1578,13 +1578,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.791689560250429</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>63.06747252081509</v>
+        <v>124.7015933934298</v>
       </c>
     </row>
     <row r="16">
@@ -1592,13 +1592,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>28.9321048441535</v>
+        <v>108.7020510573196</v>
       </c>
     </row>
     <row r="17">
@@ -1606,13 +1606,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="D17" t="n">
-        <v>6.611089040398022</v>
+        <v>84.05527494220343</v>
       </c>
     </row>
     <row r="18">
@@ -1620,13 +1620,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>4.815472489330605</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>50.82998738737861</v>
       </c>
     </row>
     <row r="19">
@@ -1637,10 +1637,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>10.23079282595601</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4.814490741626358</v>
       </c>
     </row>
     <row r="20">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1710,10 +1710,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>15.54401140133975</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="D2" t="n">
-        <v>145.8445119520892</v>
+        <v>159.5506916510789</v>
       </c>
     </row>
     <row r="3">
@@ -1721,13 +1721,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1129009859883832</v>
+        <v>0.1472621556370216</v>
       </c>
       <c r="C3" t="n">
-        <v>47.69821221083129</v>
+        <v>39.70187715974101</v>
       </c>
       <c r="D3" t="n">
-        <v>341.9869040358552</v>
+        <v>347.2637979461817</v>
       </c>
     </row>
     <row r="4">
@@ -1735,13 +1735,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.863357142660446</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C4" t="n">
-        <v>90.74294030353268</v>
+        <v>76.88262621497621</v>
       </c>
       <c r="D4" t="n">
-        <v>435.1066555313694</v>
+        <v>434.3919432026777</v>
       </c>
     </row>
     <row r="5">
@@ -1749,13 +1749,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.964739198105127</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C5" t="n">
-        <v>111.281102276376</v>
+        <v>100.8500329187536</v>
       </c>
       <c r="D5" t="n">
-        <v>301.2983704333462</v>
+        <v>312.8339059582462</v>
       </c>
     </row>
     <row r="6">
@@ -1763,13 +1763,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.85035774279376</v>
+        <v>21.45413258090555</v>
       </c>
       <c r="C6" t="n">
-        <v>150.8229545603247</v>
+        <v>131.1801464937546</v>
       </c>
       <c r="D6" t="n">
-        <v>174.3299215908104</v>
+        <v>183.9500673447249</v>
       </c>
     </row>
     <row r="7">
@@ -1777,13 +1777,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>137.5595430759503</v>
+        <v>109.6523828350305</v>
       </c>
       <c r="D7" t="n">
-        <v>127.498592602829</v>
+        <v>131.6307686900038</v>
       </c>
     </row>
     <row r="8">
@@ -1791,13 +1791,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>68.67816065058561</v>
+        <v>50.48637569089222</v>
       </c>
       <c r="D8" t="n">
-        <v>141.1115062699153</v>
+        <v>125.5900750657732</v>
       </c>
     </row>
     <row r="9">
@@ -1805,13 +1805,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>22.85312305945724</v>
+        <v>17.30624853046277</v>
       </c>
       <c r="D9" t="n">
-        <v>157.8640490951828</v>
+        <v>139.8921756212407</v>
       </c>
     </row>
     <row r="10">
@@ -1819,13 +1819,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.4164820107789</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>11.81533362061037</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D10" t="n">
-        <v>170.9664539560608</v>
+        <v>158.0122929985241</v>
       </c>
     </row>
     <row r="11">
@@ -1833,13 +1833,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.487748682561417</v>
+        <v>2.310052348092745</v>
       </c>
       <c r="C11" t="n">
-        <v>11.55026174046372</v>
+        <v>10.30638739918301</v>
       </c>
       <c r="D11" t="n">
-        <v>166.6791617316149</v>
+        <v>172.5431407690811</v>
       </c>
     </row>
     <row r="12">
@@ -1847,13 +1847,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>9.76348091873453</v>
       </c>
       <c r="D12" t="n">
-        <v>156.432660942391</v>
+        <v>181.1668126031851</v>
       </c>
     </row>
     <row r="13">
@@ -1861,13 +1861,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.325220532012953</v>
       </c>
       <c r="D13" t="n">
-        <v>116.0327611649305</v>
+        <v>171.4475103311417</v>
       </c>
     </row>
     <row r="14">
@@ -1875,13 +1875,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>9.833185005736054</v>
+        <v>7.989462817160544</v>
       </c>
       <c r="D14" t="n">
-        <v>90.03510020877073</v>
+        <v>145.346765866036</v>
       </c>
     </row>
     <row r="15">
@@ -1892,10 +1892,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>56.97572801596364</v>
+        <v>124.3432554813798</v>
       </c>
     </row>
     <row r="16">
@@ -1903,13 +1903,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>23.97231544229862</v>
+        <v>109.5286826242954</v>
       </c>
     </row>
     <row r="17">
@@ -1917,13 +1917,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>10.38885420633975</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>84.99971623368886</v>
       </c>
     </row>
     <row r="18">
@@ -1931,13 +1931,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>5.350524988145117</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>51.36503988619312</v>
       </c>
     </row>
     <row r="19">
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.619924769736241</v>
       </c>
     </row>
     <row r="20">
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.017491532227195</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2021,10 +2021,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>16.61607989437726</v>
+        <v>13.65905580918587</v>
       </c>
       <c r="D2" t="n">
-        <v>206.5803336753181</v>
+        <v>226.2967728197068</v>
       </c>
     </row>
     <row r="3">
@@ -2032,13 +2032,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.04908738521234052</v>
+        <v>0.06872233929727672</v>
       </c>
       <c r="C3" t="n">
-        <v>53.7850479771615</v>
+        <v>43.96757093469341</v>
       </c>
       <c r="D3" t="n">
-        <v>362.1961805277758</v>
+        <v>369.9519873913256</v>
       </c>
     </row>
     <row r="4">
@@ -2046,13 +2046,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.021017612416683</v>
+        <v>1.289034735676062</v>
       </c>
       <c r="C4" t="n">
-        <v>103.2248806153266</v>
+        <v>86.14836104765762</v>
       </c>
       <c r="D4" t="n">
-        <v>469.8212543535366</v>
+        <v>475.1560713784137</v>
       </c>
     </row>
     <row r="5">
@@ -2060,13 +2060,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.798602851909163</v>
+        <v>7.878525326580655</v>
       </c>
       <c r="C5" t="n">
-        <v>135.063940411755</v>
+        <v>117.2452195796754</v>
       </c>
       <c r="D5" t="n">
-        <v>343.5380654085652</v>
+        <v>355.4908437077701</v>
       </c>
     </row>
     <row r="6">
@@ -2074,13 +2074,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.15349679922777</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C6" t="n">
-        <v>161.9726632374558</v>
+        <v>142.8933783531233</v>
       </c>
       <c r="D6" t="n">
-        <v>201.540040961715</v>
+        <v>216.392901979265</v>
       </c>
     </row>
     <row r="7">
@@ -2088,13 +2088,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.17611805415445</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="C7" t="n">
-        <v>170.676838383308</v>
+        <v>140.6137601838622</v>
       </c>
       <c r="D7" t="n">
-        <v>136.4815840966873</v>
+        <v>142.8894513623063</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.10557108816892</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C8" t="n">
-        <v>113.2396889463483</v>
+        <v>85.03407740333748</v>
       </c>
       <c r="D8" t="n">
-        <v>142.7804773671348</v>
+        <v>129.9293999185441</v>
       </c>
     </row>
     <row r="9">
@@ -2116,13 +2116,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>159.9718614162007</v>
+        <v>139.4484256589212</v>
       </c>
     </row>
     <row r="10">
@@ -2130,13 +2130,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>17.36711688812608</v>
+        <v>13.95063487734718</v>
       </c>
       <c r="D10" t="n">
-        <v>171.6782210416397</v>
+        <v>158.1546464156399</v>
       </c>
     </row>
     <row r="11">
@@ -2144,13 +2144,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.665445017030089</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="C11" t="n">
-        <v>12.43874341280708</v>
+        <v>11.0171727370577</v>
       </c>
       <c r="D11" t="n">
-        <v>165.9683763937402</v>
+        <v>170.9438737588631</v>
       </c>
     </row>
     <row r="12">
@@ -2158,13 +2158,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>11.71617710248143</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>152.5272685748972</v>
+        <v>181.6007450884622</v>
       </c>
     </row>
     <row r="13">
@@ -2172,13 +2172,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>112.3904771821749</v>
+        <v>170.927184047891</v>
       </c>
     </row>
     <row r="14">
@@ -2186,13 +2186,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>10.14047203716531</v>
+        <v>8.296749848589794</v>
       </c>
       <c r="D14" t="n">
-        <v>84.81122067447346</v>
+        <v>147.4977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2203,10 +2203,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>51.24232142316227</v>
+        <v>124.3432554813798</v>
       </c>
     </row>
     <row r="16">
@@ -2214,13 +2214,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>110.3553141912712</v>
       </c>
     </row>
     <row r="17">
@@ -2228,13 +2228,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>10.38885420633975</v>
       </c>
       <c r="D17" t="n">
-        <v>3.305544520199011</v>
+        <v>84.99971623368886</v>
       </c>
     </row>
     <row r="18">
@@ -2242,13 +2242,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>5.350524988145117</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>52.97019738263666</v>
       </c>
     </row>
     <row r="19">
@@ -2259,10 +2259,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>8.425358797846126</v>
       </c>
     </row>
     <row r="20">
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2329,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.47488815141497</v>
+        <v>14.46212543125976</v>
       </c>
       <c r="C2" t="n">
-        <v>2.129410770511332</v>
+        <v>2.062651926622549</v>
       </c>
       <c r="D2" t="n">
-        <v>25.90635841966483</v>
+        <v>26.41784897357742</v>
       </c>
     </row>
     <row r="3">
@@ -2346,10 +2346,10 @@
         <v>0.3043417883165112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7755806863549802</v>
+        <v>0.7510369937488099</v>
       </c>
       <c r="D3" t="n">
-        <v>70.90181920070465</v>
+        <v>70.17041716104077</v>
       </c>
     </row>
     <row r="4">
@@ -2357,13 +2357,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.467712817848982</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="C4" t="n">
-        <v>3.012001956629214</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="D4" t="n">
-        <v>152.9484383400191</v>
+        <v>151.8891325671368</v>
       </c>
     </row>
     <row r="5">
@@ -2371,13 +2371,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>4.147884050442775</v>
+        <v>4.172427743048945</v>
       </c>
       <c r="D5" t="n">
-        <v>85.73111827335273</v>
+        <v>90.0508081720387</v>
       </c>
     </row>
     <row r="6">
@@ -2388,10 +2388,10 @@
         <v>4.628940425523712</v>
       </c>
       <c r="C6" t="n">
-        <v>5.031456984264904</v>
+        <v>4.991205328390785</v>
       </c>
       <c r="D6" t="n">
-        <v>106.344874819423</v>
+        <v>104.4127953374653</v>
       </c>
     </row>
     <row r="7">
@@ -2399,13 +2399,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
         <v>6.886960145291375</v>
       </c>
       <c r="D7" t="n">
-        <v>147.0216274494811</v>
+        <v>144.5662764411598</v>
       </c>
     </row>
     <row r="8">
@@ -2416,10 +2416,10 @@
         <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>8.678649705541805</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="D8" t="n">
-        <v>185.923380230261</v>
+        <v>183.6702692490145</v>
       </c>
     </row>
     <row r="9">
@@ -2427,13 +2427,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>9.096874227550941</v>
       </c>
       <c r="C9" t="n">
-        <v>10.42812411450962</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="D9" t="n">
-        <v>225.4249808583355</v>
+        <v>221.0984187257199</v>
       </c>
     </row>
     <row r="10">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>11.95768703772615</v>
+        <v>11.81533362061037</v>
       </c>
       <c r="D10" t="n">
-        <v>251.1114277922492</v>
+        <v>252.6773153805228</v>
       </c>
     </row>
     <row r="11">
@@ -2458,10 +2458,10 @@
         <v>10.48408373365169</v>
       </c>
       <c r="C11" t="n">
-        <v>12.9718324162131</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>281.8263864673148</v>
+        <v>279.1609414502847</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2475,7 @@
         <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>290.5177988930119</v>
+        <v>292.6874613193973</v>
       </c>
     </row>
     <row r="13">
@@ -2483,13 +2483,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.40652566501619</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="C13" t="n">
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>298.6672865859647</v>
+        <v>299.1876128692155</v>
       </c>
     </row>
     <row r="14">
@@ -2497,13 +2497,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>297.1465593920864</v>
+        <v>300.8340037692374</v>
       </c>
     </row>
     <row r="15">
@@ -2514,10 +2514,10 @@
         <v>12.541826921753</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>303.5122115064227</v>
+        <v>302.7955356823225</v>
       </c>
     </row>
     <row r="16">
@@ -2525,13 +2525,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>290.5609957919987</v>
+        <v>302.547153513148</v>
       </c>
     </row>
     <row r="17">
@@ -2542,10 +2542,10 @@
         <v>14.16661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>23.61103228713579</v>
+        <v>22.66659099565036</v>
       </c>
       <c r="D17" t="n">
-        <v>248.3880596606685</v>
+        <v>257.8324725755228</v>
       </c>
     </row>
     <row r="18">
@@ -2556,10 +2556,10 @@
         <v>15.51652246562084</v>
       </c>
       <c r="C18" t="n">
-        <v>26.75262494072559</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>211.8807895305466</v>
+        <v>229.002469492611</v>
       </c>
     </row>
     <row r="19">
@@ -2567,13 +2567,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
       <c r="C19" t="n">
-        <v>30.09056713516474</v>
+        <v>29.48875579246144</v>
       </c>
       <c r="D19" t="n">
-        <v>160.6836285017797</v>
+        <v>182.3488368390983</v>
       </c>
     </row>
     <row r="20">
@@ -2584,10 +2584,10 @@
         <v>16.81242943522663</v>
       </c>
       <c r="C20" t="n">
-        <v>37.65984193490764</v>
+        <v>32.27986451563512</v>
       </c>
       <c r="D20" t="n">
-        <v>75.99218104722434</v>
+        <v>124.411977820677</v>
       </c>
     </row>
     <row r="21">
@@ -2595,13 +2595,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>9.392969336671905</v>
+        <v>18.06689606826397</v>
       </c>
       <c r="C21" t="n">
-        <v>22.39861918744839</v>
+        <v>39.89772881741627</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.258362008532996</v>
       </c>
     </row>
   </sheetData>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>8.933904108645974</v>
+        <v>8.615817852470007</v>
       </c>
       <c r="D2" t="n">
-        <v>96.68447740963438</v>
+        <v>99.05932510620742</v>
       </c>
     </row>
     <row r="3">
@@ -2654,13 +2654,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.16295442337174</v>
+        <v>21.56408832378119</v>
       </c>
       <c r="C3" t="n">
-        <v>3.701188845010475</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="D3" t="n">
-        <v>72.30080967925635</v>
+        <v>71.19143477345746</v>
       </c>
     </row>
     <row r="4">
@@ -2668,13 +2668,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.059305772882309</v>
+        <v>1.033780332571891</v>
       </c>
       <c r="C4" t="n">
-        <v>2.565306751196915</v>
+        <v>2.552544031041707</v>
       </c>
       <c r="D4" t="n">
-        <v>151.0085048764274</v>
+        <v>148.7367406888003</v>
       </c>
     </row>
     <row r="5">
@@ -2682,13 +2682,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.748893571891069</v>
+        <v>2.699806186678729</v>
       </c>
       <c r="C5" t="n">
-        <v>4.61421420996001</v>
+        <v>4.63875790256618</v>
       </c>
       <c r="D5" t="n">
-        <v>99.10743074371554</v>
+        <v>106.6914317590221</v>
       </c>
     </row>
     <row r="6">
@@ -2699,10 +2699,10 @@
         <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>5.554728510628454</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="D6" t="n">
-        <v>108.4379609248772</v>
+        <v>105.8618549489336</v>
       </c>
     </row>
     <row r="7">
@@ -2710,13 +2710,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>7.066619975168541</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="D7" t="n">
-        <v>147.5007203291535</v>
+        <v>144.0272969515283</v>
       </c>
     </row>
     <row r="8">
@@ -2724,13 +2724,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>9.012443924985718</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="D8" t="n">
-        <v>186.3406230045658</v>
+        <v>181.3337097129071</v>
       </c>
     </row>
     <row r="9">
@@ -2738,13 +2738,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.985936736971052</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.53906160508951</v>
       </c>
       <c r="D9" t="n">
-        <v>229.0859180474719</v>
+        <v>218.4359189518025</v>
       </c>
     </row>
     <row r="10">
@@ -2752,13 +2752,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.680032363873552</v>
       </c>
       <c r="C10" t="n">
-        <v>12.38474728907351</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="D10" t="n">
-        <v>249.6878936210913</v>
+        <v>252.3926085462913</v>
       </c>
     </row>
     <row r="11">
@@ -2769,10 +2769,10 @@
         <v>10.30638739918301</v>
       </c>
       <c r="C11" t="n">
-        <v>13.50492141961912</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>280.9379047949715</v>
+        <v>275.9624074298486</v>
       </c>
     </row>
     <row r="12">
@@ -2783,10 +2783,10 @@
         <v>10.19741340401162</v>
       </c>
       <c r="C12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>288.565102709265</v>
+        <v>292.9044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2794,13 +2794,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="C13" t="n">
         <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>294.7648394615836</v>
+        <v>296.0656551697106</v>
       </c>
     </row>
     <row r="14">
@@ -2808,13 +2808,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>293.7664020463646</v>
+        <v>300.8340037692374</v>
       </c>
     </row>
     <row r="15">
@@ -2825,10 +2825,10 @@
         <v>11.82515109765283</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>298.4954807377214</v>
+        <v>298.8538186497715</v>
       </c>
     </row>
     <row r="16">
@@ -2836,13 +2836,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>275.681627586434</v>
+        <v>301.7205219461723</v>
       </c>
     </row>
     <row r="17">
@@ -2850,13 +2850,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>24.0832529328785</v>
+        <v>22.19437034990765</v>
       </c>
       <c r="D17" t="n">
-        <v>236.1103228713579</v>
+        <v>255.943589992552</v>
       </c>
     </row>
     <row r="18">
@@ -2867,10 +2867,10 @@
         <v>14.44641746799181</v>
       </c>
       <c r="C18" t="n">
-        <v>27.28767743954009</v>
+        <v>25.68251994309656</v>
       </c>
       <c r="D18" t="n">
-        <v>195.2941620672968</v>
+        <v>229.002469492611</v>
       </c>
     </row>
     <row r="19">
@@ -2878,13 +2878,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15.64709491028566</v>
+        <v>14.44347222487907</v>
       </c>
       <c r="C19" t="n">
-        <v>31.29418982057133</v>
+        <v>28.88694444975815</v>
       </c>
       <c r="D19" t="n">
-        <v>129.9912500239116</v>
+        <v>180.5434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -2892,13 +2892,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>18.15742379004475</v>
+        <v>15.46743508040849</v>
       </c>
       <c r="C20" t="n">
-        <v>51.10978548308893</v>
+        <v>31.60736733822606</v>
       </c>
       <c r="D20" t="n">
-        <v>46.40230524122548</v>
+        <v>125.0844749980861</v>
       </c>
     </row>
     <row r="21">
@@ -2906,13 +2906,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>18.21711644922847</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>42.50660504819977</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4.554279112307118</v>
       </c>
     </row>
   </sheetData>
@@ -2951,13 +2951,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.241330008795468</v>
+        <v>2.260964962880404</v>
       </c>
       <c r="C2" t="n">
-        <v>6.134941403838318</v>
+        <v>5.935646619876215</v>
       </c>
       <c r="D2" t="n">
-        <v>104.0623114070492</v>
+        <v>106.5962022317102</v>
       </c>
     </row>
     <row r="3">
@@ -2965,13 +2965,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.89387343695011</v>
+        <v>11.75642875835555</v>
       </c>
       <c r="C3" t="n">
-        <v>15.81595551541612</v>
+        <v>14.86856898081794</v>
       </c>
       <c r="D3" t="n">
-        <v>101.8317806230004</v>
+        <v>101.1298310144639</v>
       </c>
     </row>
     <row r="4">
@@ -2979,13 +2979,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.74843590800134</v>
+        <v>17.76570645605028</v>
       </c>
       <c r="C4" t="n">
-        <v>4.990223580686537</v>
+        <v>4.824308218668826</v>
       </c>
       <c r="D4" t="n">
-        <v>149.6046056593544</v>
+        <v>146.273535698845</v>
       </c>
     </row>
     <row r="5">
@@ -2993,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2.307107104980005</v>
+        <v>2.258019719767664</v>
       </c>
       <c r="C5" t="n">
         <v>4.61421420996001</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7656847316464</v>
+        <v>120.656792851933</v>
       </c>
     </row>
     <row r="6">
@@ -3007,13 +3007,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.22642386678252</v>
+        <v>4.145920555034281</v>
       </c>
       <c r="C6" t="n">
-        <v>6.158503348740243</v>
+        <v>6.037748381117884</v>
       </c>
       <c r="D6" t="n">
-        <v>111.8593516741773</v>
+        <v>109.5247556334784</v>
       </c>
     </row>
     <row r="7">
@@ -3021,13 +3021,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>7.425939634922873</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="D7" t="n">
-        <v>146.6623077897268</v>
+        <v>143.727863901733</v>
       </c>
     </row>
     <row r="8">
@@ -3035,13 +3035,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.42692138262712</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>9.179341034707678</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="D8" t="n">
-        <v>187.0082114434537</v>
+        <v>179.1640472865217</v>
       </c>
     </row>
     <row r="9">
@@ -3049,13 +3049,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>11.09374905798895</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="D9" t="n">
-        <v>235.0765425387859</v>
+        <v>217.8812314989031</v>
       </c>
     </row>
     <row r="10">
@@ -3063,13 +3063,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>12.81180754042088</v>
+        <v>12.24239387195773</v>
       </c>
       <c r="D10" t="n">
-        <v>248.2643594499334</v>
+        <v>249.1184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3077,13 +3077,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10.12869106471434</v>
+        <v>9.950994730245668</v>
       </c>
       <c r="C11" t="n">
-        <v>14.03801042302514</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>280.0494231226281</v>
+        <v>273.1192660783499</v>
       </c>
     </row>
     <row r="12">
@@ -3094,10 +3094,10 @@
         <v>9.980447161373073</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>286.6124065255181</v>
+        <v>292.9044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -3105,13 +3105,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>291.122555478828</v>
+        <v>293.2038606118312</v>
       </c>
     </row>
     <row r="14">
@@ -3119,13 +3119,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.36962016288231</v>
+        <v>9.833185005736054</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>290.0789576692136</v>
+        <v>300.5267167378081</v>
       </c>
     </row>
     <row r="15">
@@ -3133,13 +3133,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11.10847527355266</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>16.84188186635403</v>
       </c>
       <c r="D15" t="n">
-        <v>291.6870604087698</v>
+        <v>295.2704395292707</v>
       </c>
     </row>
     <row r="16">
@@ -3147,13 +3147,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.5728419376614</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>261.6288909478452</v>
+        <v>300.4805745957085</v>
       </c>
     </row>
     <row r="17">
@@ -3161,13 +3161,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12.74995743505333</v>
+        <v>12.27773678931061</v>
       </c>
       <c r="C17" t="n">
-        <v>24.55547357862122</v>
+        <v>22.19437034990765</v>
       </c>
       <c r="D17" t="n">
-        <v>222.8881447905619</v>
+        <v>254.0547074095811</v>
       </c>
     </row>
     <row r="18">
@@ -3175,13 +3175,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
       <c r="C18" t="n">
-        <v>27.82272993835461</v>
+        <v>25.14746744428205</v>
       </c>
       <c r="D18" t="n">
-        <v>173.8920621147163</v>
+        <v>229.002469492611</v>
       </c>
     </row>
     <row r="19">
@@ -3189,13 +3189,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>28.28513310705485</v>
       </c>
       <c r="D19" t="n">
-        <v>101.1043055741535</v>
+        <v>178.7379687828785</v>
       </c>
     </row>
     <row r="20">
@@ -3203,13 +3203,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10.75995483854504</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>41.69482499936203</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>28.24488145118073</v>
+        <v>125.7569721754952</v>
       </c>
     </row>
     <row r="21">
@@ -3217,13 +3217,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>17.59886628379263</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>45.14491785842458</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6.886512893657987</v>
       </c>
     </row>
   </sheetData>
@@ -3262,13 +3262,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5762859023928777</v>
+        <v>1.151590057081509</v>
       </c>
       <c r="C2" t="n">
-        <v>10.95335913628166</v>
+        <v>10.28773419280233</v>
       </c>
       <c r="D2" t="n">
-        <v>173.2657070794068</v>
+        <v>177.4636602627662</v>
       </c>
     </row>
     <row r="3">
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.788024611340701</v>
+        <v>9.665306148309849</v>
       </c>
       <c r="C3" t="n">
-        <v>18.98209186161208</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="D3" t="n">
-        <v>130.5822621418683</v>
+        <v>130.0128484734051</v>
       </c>
     </row>
     <row r="4">
@@ -3290,13 +3290,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.12680968476386</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="C4" t="n">
-        <v>18.05924901962008</v>
+        <v>16.36180723897734</v>
       </c>
       <c r="D4" t="n">
-        <v>155.0032362850077</v>
+        <v>151.6211154438774</v>
       </c>
     </row>
     <row r="5">
@@ -3304,13 +3304,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.17367153266045</v>
+        <v>11.29009859883832</v>
       </c>
       <c r="C5" t="n">
-        <v>6.185010536754907</v>
+        <v>6.062292073724056</v>
       </c>
       <c r="D5" t="n">
-        <v>120.9758608558132</v>
+        <v>132.3886779176824</v>
       </c>
     </row>
     <row r="6">
@@ -3318,13 +3318,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3.864158963915446</v>
+        <v>3.743403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>6.561019907481435</v>
+        <v>6.440264939859078</v>
       </c>
       <c r="D6" t="n">
-        <v>116.3272854762046</v>
+        <v>114.7574708971139</v>
       </c>
     </row>
     <row r="7">
@@ -3332,13 +3332,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>7.964919124554372</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="D7" t="n">
-        <v>146.1233283000953</v>
+        <v>143.9075237316102</v>
       </c>
     </row>
     <row r="8">
@@ -3346,13 +3346,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="D8" t="n">
-        <v>187.5923513274805</v>
+        <v>177.1612819698582</v>
       </c>
     </row>
     <row r="9">
@@ -3360,13 +3360,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>11.31562403914873</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="D9" t="n">
-        <v>238.959354709082</v>
+        <v>217.2156065554237</v>
       </c>
     </row>
     <row r="10">
@@ -3374,13 +3374,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.680032363873552</v>
+        <v>9.110618695410402</v>
       </c>
       <c r="C10" t="n">
-        <v>13.23886779176824</v>
+        <v>12.66945412330509</v>
       </c>
       <c r="D10" t="n">
-        <v>249.4031867868597</v>
+        <v>246.1290581931966</v>
       </c>
     </row>
     <row r="11">
@@ -3388,13 +3388,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.950994730245668</v>
+        <v>9.773298395776996</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>278.983245115816</v>
+        <v>272.7638734094125</v>
       </c>
     </row>
     <row r="12">
@@ -3405,10 +3405,10 @@
         <v>9.76348091873453</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>282.0561154301086</v>
+        <v>289.2160014371806</v>
       </c>
     </row>
     <row r="13">
@@ -3416,13 +3416,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>290.3420660539517</v>
+        <v>290.6022291955771</v>
       </c>
     </row>
     <row r="14">
@@ -3430,13 +3430,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11.06233313145306</v>
+        <v>9.525897974306801</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>286.0842262606333</v>
+        <v>299.9121426749496</v>
       </c>
     </row>
     <row r="15">
@@ -3444,13 +3444,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10.75013736150257</v>
+        <v>10.0334615374024</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>16.84188186635403</v>
       </c>
       <c r="D15" t="n">
-        <v>281.6535988713674</v>
+        <v>292.0453983208199</v>
       </c>
     </row>
     <row r="16">
@@ -3458,13 +3458,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11.5728419376614</v>
+        <v>10.74621037068559</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>250.8826805771596</v>
+        <v>299.2406272452448</v>
       </c>
     </row>
     <row r="17">
@@ -3472,13 +3472,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="C17" t="n">
-        <v>25.49991487010665</v>
+        <v>21.72214970416493</v>
       </c>
       <c r="D17" t="n">
-        <v>207.777084126795</v>
+        <v>252.1658248266102</v>
       </c>
     </row>
     <row r="18">
@@ -3486,13 +3486,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13.37631247036279</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>24.61241494546753</v>
       </c>
       <c r="D18" t="n">
-        <v>150.8848046656923</v>
+        <v>228.4674169937965</v>
       </c>
     </row>
     <row r="19">
@@ -3500,13 +3500,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13.23984953947248</v>
+        <v>12.63803819676919</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>27.68332176435156</v>
       </c>
       <c r="D19" t="n">
-        <v>76.43004052331844</v>
+        <v>176.9325347547687</v>
       </c>
     </row>
     <row r="20">
@@ -3514,13 +3514,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.052474596681584</v>
+        <v>12.77744637077223</v>
       </c>
       <c r="C20" t="n">
-        <v>34.29735604786232</v>
+        <v>30.93487016081699</v>
       </c>
       <c r="D20" t="n">
-        <v>16.81242943522663</v>
+        <v>126.4294693529042</v>
       </c>
     </row>
     <row r="21">
@@ -3528,13 +3528,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>16.96681374010626</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>47.04434718847646</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>9.254625676421599</v>
       </c>
     </row>
   </sheetData>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.466150233067987</v>
+        <v>2.981567777797563</v>
       </c>
       <c r="C2" t="n">
-        <v>8.115126523304134</v>
+        <v>7.71948219849267</v>
       </c>
       <c r="D2" t="n">
-        <v>166.2128315720977</v>
+        <v>170.1192056872958</v>
       </c>
     </row>
     <row r="3">
@@ -3587,13 +3587,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.952917167925158</v>
+        <v>5.738315331322607</v>
       </c>
       <c r="C3" t="n">
-        <v>26.10467145592269</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="D3" t="n">
-        <v>173.0821202587127</v>
+        <v>173.1361163824463</v>
       </c>
     </row>
     <row r="4">
@@ -3601,13 +3601,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.41361888312417</v>
+        <v>12.94139823738145</v>
       </c>
       <c r="C4" t="n">
-        <v>24.26193101505142</v>
+        <v>21.58175978245763</v>
       </c>
       <c r="D4" t="n">
-        <v>143.5678390259408</v>
+        <v>142.6489231747658</v>
       </c>
     </row>
     <row r="5">
@@ -3615,13 +3615,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.83005983617407</v>
+        <v>10.87285582453343</v>
       </c>
       <c r="C5" t="n">
-        <v>12.07549676223577</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="D5" t="n">
-        <v>106.519625910779</v>
+        <v>114.6435881634213</v>
       </c>
     </row>
     <row r="6">
@@ -3629,13 +3629,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.910702016642547</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>5.313218575383739</v>
+        <v>5.152211951887262</v>
       </c>
       <c r="D6" t="n">
-        <v>94.95365620704727</v>
+        <v>95.55743104515906</v>
       </c>
     </row>
     <row r="7">
@@ -3643,13 +3643,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.75478405811655</v>
+        <v>2.635010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>5.569454726192155</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="D7" t="n">
-        <v>110.3111355445801</v>
+        <v>108.2749908059722</v>
       </c>
     </row>
     <row r="8">
@@ -3657,13 +3657,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.421390749300134</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C8" t="n">
-        <v>6.342090169434394</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="D8" t="n">
-        <v>138.7749467338079</v>
+        <v>129.5121571442392</v>
       </c>
     </row>
     <row r="9">
@@ -3671,13 +3671,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.882812170296134</v>
+        <v>3.771874679716245</v>
       </c>
       <c r="C9" t="n">
-        <v>7.21093688769282</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="D9" t="n">
-        <v>177.0562349655037</v>
+        <v>156.7546741893839</v>
       </c>
     </row>
     <row r="10">
@@ -3685,13 +3685,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>8.114144775599888</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="D10" t="n">
-        <v>176.5182372235765</v>
+        <v>173.528815464145</v>
       </c>
     </row>
     <row r="11">
@@ -3699,13 +3699,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="D11" t="n">
-        <v>195.2882715810712</v>
+        <v>191.7343448916978</v>
       </c>
     </row>
     <row r="12">
@@ -3713,13 +3713,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>8.895615948180348</v>
+        <v>8.678649705541803</v>
       </c>
       <c r="D12" t="n">
-        <v>194.8356858894135</v>
+        <v>199.1750107421844</v>
       </c>
     </row>
     <row r="13">
@@ -3727,13 +3727,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.902447124381071</v>
+        <v>3.642283982755667</v>
       </c>
       <c r="C13" t="n">
-        <v>8.845546815263763</v>
+        <v>8.585383673638358</v>
       </c>
       <c r="D13" t="n">
-        <v>197.2036613520568</v>
+        <v>200.8459453348125</v>
       </c>
     </row>
     <row r="14">
@@ -3741,13 +3741,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>9.21861094287755</v>
+        <v>8.604036880019047</v>
       </c>
       <c r="D14" t="n">
-        <v>192.3616816747115</v>
+        <v>202.5021537118768</v>
       </c>
     </row>
     <row r="15">
@@ -3755,13 +3755,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>10.39179944945249</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>185.9773763539945</v>
+        <v>198.5192032757475</v>
       </c>
     </row>
     <row r="16">
@@ -3769,13 +3769,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.133157834879071</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="D16" t="n">
-        <v>159.9532082098201</v>
+        <v>199.2182076411713</v>
       </c>
     </row>
     <row r="17">
@@ -3783,13 +3783,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.249985811684442</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="D17" t="n">
-        <v>128.4440156420187</v>
+        <v>168.5827705301495</v>
       </c>
     </row>
     <row r="18">
@@ -3797,13 +3797,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>13.37631247036279</v>
       </c>
       <c r="D18" t="n">
-        <v>85.07334731150736</v>
+        <v>152.4899621621358</v>
       </c>
     </row>
     <row r="19">
@@ -3811,13 +3811,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>14.44347222487907</v>
       </c>
       <c r="D19" t="n">
-        <v>37.31230324760427</v>
+        <v>116.7514004844392</v>
       </c>
     </row>
     <row r="20">
@@ -3825,13 +3825,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>14.79493790299943</v>
+        <v>16.13993225781756</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>84.06214717613311</v>
       </c>
     </row>
     <row r="21">
@@ -3839,13 +3839,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>6.216252853391196</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>26.41907462691259</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7.770316066738995</v>
       </c>
     </row>
   </sheetData>
@@ -3887,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>7.094108910887452</v>
+        <v>6.663121668723102</v>
       </c>
       <c r="D2" t="n">
-        <v>180.3146555958989</v>
+        <v>186.8737120079718</v>
       </c>
     </row>
     <row r="3">
@@ -3898,13 +3898,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.083309686140737</v>
+        <v>8.315403054970485</v>
       </c>
       <c r="C3" t="n">
-        <v>29.08427573831176</v>
+        <v>26.6397239547372</v>
       </c>
       <c r="D3" t="n">
-        <v>230.9855998551895</v>
+        <v>233.0619962496716</v>
       </c>
     </row>
     <row r="4">
@@ -3912,13 +3912,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.42263453891164</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C4" t="n">
-        <v>44.68228326338508</v>
+        <v>39.75587328347459</v>
       </c>
       <c r="D4" t="n">
-        <v>178.8184720946268</v>
+        <v>176.687097828707</v>
       </c>
     </row>
     <row r="5">
@@ -3926,13 +3926,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.32155558310323</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="C5" t="n">
-        <v>27.75891633757857</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="D5" t="n">
-        <v>121.1722103966626</v>
+        <v>128.437143408089</v>
       </c>
     </row>
     <row r="6">
@@ -3940,13 +3940,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>9.539642442166258</v>
       </c>
       <c r="C6" t="n">
-        <v>11.63272854762046</v>
+        <v>10.10316562440393</v>
       </c>
       <c r="D6" t="n">
-        <v>102.3599608878852</v>
+        <v>104.976318519703</v>
       </c>
     </row>
     <row r="7">
@@ -3954,13 +3954,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.371722527011046</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>6.527640485537042</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="D7" t="n">
-        <v>111.5687543537203</v>
+        <v>109.7122694449895</v>
       </c>
     </row>
     <row r="8">
@@ -3968,13 +3968,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.421390749300134</v>
+        <v>3.171045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>6.926230053461247</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="D8" t="n">
-        <v>139.6928808372786</v>
+        <v>130.43009124771</v>
       </c>
     </row>
     <row r="9">
@@ -3982,13 +3982,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.882812170296134</v>
+        <v>3.660937189136355</v>
       </c>
       <c r="C9" t="n">
-        <v>7.654686850012379</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="D9" t="n">
-        <v>179.0531097959417</v>
+        <v>155.0906118306856</v>
       </c>
     </row>
     <row r="10">
@@ -3996,13 +3996,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="D10" t="n">
-        <v>180.5041329028186</v>
+        <v>174.3829359668397</v>
       </c>
     </row>
     <row r="11">
@@ -4010,13 +4010,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>9.417905726839649</v>
+        <v>8.529424054496287</v>
       </c>
       <c r="D11" t="n">
-        <v>195.2882715810712</v>
+        <v>191.9120412261665</v>
       </c>
     </row>
     <row r="12">
@@ -4024,13 +4024,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>9.546514676095983</v>
+        <v>8.895615948180348</v>
       </c>
       <c r="D12" t="n">
-        <v>194.1847871614979</v>
+        <v>197.8732132863531</v>
       </c>
     </row>
     <row r="13">
@@ -4038,13 +4038,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.902447124381071</v>
+        <v>3.642283982755667</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
       <c r="D13" t="n">
-        <v>195.1223562190536</v>
+        <v>201.6264347596887</v>
       </c>
     </row>
     <row r="14">
@@ -4052,13 +4052,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3.994731408580272</v>
+        <v>3.380157345721768</v>
       </c>
       <c r="C14" t="n">
-        <v>9.525897974306801</v>
+        <v>8.911323911448299</v>
       </c>
       <c r="D14" t="n">
-        <v>189.5960983918483</v>
+        <v>200.6584315233014</v>
       </c>
     </row>
     <row r="15">
@@ -4066,13 +4066,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.583379120500858</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>10.39179944945249</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>180.9606455852933</v>
+        <v>198.8775411877976</v>
       </c>
     </row>
     <row r="16">
@@ -4080,13 +4080,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.133157834879071</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="D16" t="n">
-        <v>152.5135241070377</v>
+        <v>196.7383129402438</v>
       </c>
     </row>
     <row r="17">
@@ -4094,13 +4094,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3.777765165941727</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>11.33329549782518</v>
       </c>
       <c r="D17" t="n">
-        <v>117.1107201441935</v>
+        <v>169.9994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -4108,13 +4108,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.280419990516093</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="D18" t="n">
-        <v>71.16198234233005</v>
+        <v>152.4899621621358</v>
       </c>
     </row>
     <row r="19">
@@ -4122,13 +4122,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.407245370813179</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>14.44347222487907</v>
       </c>
       <c r="D19" t="n">
-        <v>27.08151042164826</v>
+        <v>116.1495891417359</v>
       </c>
     </row>
     <row r="20">
@@ -4136,13 +4136,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>13.4499435481813</v>
+        <v>15.46743508040849</v>
       </c>
       <c r="D20" t="n">
-        <v>4.03498306445439</v>
+        <v>84.73464435354219</v>
       </c>
     </row>
     <row r="21">
@@ -4150,13 +4150,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>6.286134523738546</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>28.28760535682346</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>10.21496860107514</v>
       </c>
     </row>
   </sheetData>
@@ -4198,10 +4198,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3.858268477689965</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="D2" t="n">
-        <v>138.4902398995763</v>
+        <v>143.5285691177709</v>
       </c>
     </row>
     <row r="3">
@@ -4209,13 +4209,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.829437941368314</v>
+        <v>9.056622571676826</v>
       </c>
       <c r="C3" t="n">
-        <v>35.86815237465722</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D3" t="n">
-        <v>261.1596155452153</v>
+        <v>264.0754062268283</v>
       </c>
     </row>
     <row r="4">
@@ -4223,13 +4223,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.89034735676062</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C4" t="n">
-        <v>52.88871232318417</v>
+        <v>44.14624901686633</v>
       </c>
       <c r="D4" t="n">
-        <v>168.9911775751162</v>
+        <v>168.123312604562</v>
       </c>
     </row>
     <row r="5">
@@ -4237,13 +4237,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5.988660995905544</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C5" t="n">
-        <v>20.00310947402876</v>
+        <v>16.49336143134642</v>
       </c>
       <c r="D5" t="n">
-        <v>115.7235106380928</v>
+        <v>121.0249482410256</v>
       </c>
     </row>
     <row r="6">
@@ -4251,13 +4251,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.696860943565988</v>
+        <v>2.455351008321273</v>
       </c>
       <c r="C6" t="n">
-        <v>4.266675522656639</v>
+        <v>4.065417243286043</v>
       </c>
       <c r="D6" t="n">
-        <v>96.52347078613792</v>
+        <v>97.97253039760622</v>
       </c>
     </row>
     <row r="7">
@@ -4265,13 +4265,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.215804568485051</v>
+        <v>2.09603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>4.850815406683489</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="D7" t="n">
-        <v>98.2140403328509</v>
+        <v>91.68639984731387</v>
       </c>
     </row>
     <row r="8">
@@ -4279,13 +4279,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.670353755551324</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="D8" t="n">
-        <v>131.9321652352076</v>
+        <v>114.3245201595411</v>
       </c>
     </row>
     <row r="9">
@@ -4293,13 +4293,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="D9" t="n">
-        <v>137.7843633002228</v>
+        <v>133.1249886958674</v>
       </c>
     </row>
     <row r="10">
@@ -4307,13 +4307,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>7.260024272905163</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="D10" t="n">
-        <v>153.3146302337032</v>
+        <v>150.6099153085032</v>
       </c>
     </row>
     <row r="11">
@@ -4321,13 +4321,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="D11" t="n">
-        <v>155.8396853290259</v>
+        <v>158.6828266805247</v>
       </c>
     </row>
     <row r="12">
@@ -4335,13 +4335,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="C12" t="n">
-        <v>7.593818492349078</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="D12" t="n">
-        <v>159.4701883393306</v>
+        <v>164.6773781626557</v>
       </c>
     </row>
     <row r="13">
@@ -4349,13 +4349,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>7.804894248762142</v>
+        <v>7.284567965511334</v>
       </c>
       <c r="D13" t="n">
-        <v>157.1385375417445</v>
+        <v>166.2442474986337</v>
       </c>
     </row>
     <row r="14">
@@ -4363,13 +4363,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.765583282863265</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>8.604036880019047</v>
+        <v>7.682175785731292</v>
       </c>
       <c r="D14" t="n">
-        <v>151.7997935260503</v>
+        <v>166.8568580660836</v>
       </c>
     </row>
     <row r="15">
@@ -4377,13 +4377,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3.225041208450772</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>10.75013736150257</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>129.359986250081</v>
+        <v>166.98546701534</v>
       </c>
     </row>
     <row r="16">
@@ -4391,13 +4391,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.89321048441535</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="D16" t="n">
-        <v>100.4357353875614</v>
+        <v>145.4871557877433</v>
       </c>
     </row>
     <row r="17">
@@ -4405,13 +4405,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3.305544520199011</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="D17" t="n">
-        <v>61.38868394655305</v>
+        <v>131.7495601622177</v>
       </c>
     </row>
     <row r="18">
@@ -4419,13 +4419,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="D18" t="n">
-        <v>23.54230994783851</v>
+        <v>101.1249222759427</v>
       </c>
     </row>
     <row r="19">
@@ -4433,13 +4433,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>11.4344155113626</v>
+        <v>13.23984953947248</v>
       </c>
       <c r="D19" t="n">
-        <v>3.009056713516474</v>
+        <v>74.02279515250525</v>
       </c>
     </row>
     <row r="20">
@@ -4447,13 +4447,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>23.53740120931727</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>8.06996612890878</v>
       </c>
     </row>
     <row r="21">
@@ -4509,10 +4509,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.743583922742335</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="D2" t="n">
-        <v>103.4241753992887</v>
+        <v>108.7491749471234</v>
       </c>
     </row>
     <row r="3">
@@ -4520,13 +4520,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3.735550014659113</v>
+        <v>4.471860792844221</v>
       </c>
       <c r="C3" t="n">
-        <v>25.54998400302324</v>
+        <v>24.58787125286137</v>
       </c>
       <c r="D3" t="n">
-        <v>300.6847781181918</v>
+        <v>297.7248087898877</v>
       </c>
     </row>
     <row r="4">
@@ -4534,13 +4534,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.86856898081794</v>
+        <v>15.63433219013046</v>
       </c>
       <c r="C4" t="n">
-        <v>73.19420009012096</v>
+        <v>64.24753326131977</v>
       </c>
       <c r="D4" t="n">
-        <v>220.9482113269702</v>
+        <v>225.9639603479671</v>
       </c>
     </row>
     <row r="5">
@@ -4548,13 +4548,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.53553552490002</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C5" t="n">
-        <v>55.0515025156399</v>
+        <v>43.85957868722626</v>
       </c>
       <c r="D5" t="n">
-        <v>131.603279754285</v>
+        <v>137.1256105906733</v>
       </c>
     </row>
     <row r="6">
@@ -4562,13 +4562,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4.347178834404877</v>
+        <v>3.783655652167208</v>
       </c>
       <c r="C6" t="n">
-        <v>14.69185439405352</v>
+        <v>11.83398682699105</v>
       </c>
       <c r="D6" t="n">
-        <v>105.0970734873253</v>
+        <v>106.7071397222901</v>
       </c>
     </row>
     <row r="7">
@@ -4576,13 +4576,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.575124228239384</v>
+        <v>2.395464398362217</v>
       </c>
       <c r="C7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="D7" t="n">
-        <v>102.5258762499029</v>
+        <v>97.31574118346508</v>
       </c>
     </row>
     <row r="8">
@@ -4590,13 +4590,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.920699420134261</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="C8" t="n">
-        <v>6.926230053461247</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D8" t="n">
-        <v>136.1045929782565</v>
+        <v>118.7472935671729</v>
       </c>
     </row>
     <row r="9">
@@ -4604,13 +4604,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>7.321874378272709</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>145.1062376784955</v>
+        <v>140.55780056472</v>
       </c>
     </row>
     <row r="10">
@@ -4618,13 +4618,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="D10" t="n">
-        <v>160.2899476723767</v>
+        <v>157.442879330061</v>
       </c>
     </row>
     <row r="11">
@@ -4632,13 +4632,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.132356013624072</v>
+        <v>1.954659679155399</v>
       </c>
       <c r="C11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="D11" t="n">
-        <v>167.2122507350209</v>
+        <v>169.877695752051</v>
       </c>
     </row>
     <row r="12">
@@ -4646,13 +4646,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="D12" t="n">
-        <v>170.9693991991735</v>
+        <v>178.9971501767997</v>
       </c>
     </row>
     <row r="13">
@@ -4660,13 +4660,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>7.024404823885929</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="D13" t="n">
-        <v>128.7807551045754</v>
+        <v>167.5450632067607</v>
       </c>
     </row>
     <row r="14">
@@ -4674,13 +4674,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.458296251434013</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>8.911323911448299</v>
+        <v>7.067601722872788</v>
       </c>
       <c r="D14" t="n">
-        <v>108.4723220945258</v>
+        <v>140.1228863317388</v>
       </c>
     </row>
     <row r="15">
@@ -4688,13 +4688,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.150027472300515</v>
+        <v>1.791689560250429</v>
       </c>
       <c r="C15" t="n">
-        <v>10.0334615374024</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>85.28442306792041</v>
+        <v>123.2682417452295</v>
       </c>
     </row>
     <row r="16">
@@ -4702,13 +4702,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.479894700927443</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>9.092947236733956</v>
       </c>
       <c r="D16" t="n">
-        <v>52.49110450296421</v>
+        <v>112.8352088921987</v>
       </c>
     </row>
     <row r="17">
@@ -4716,13 +4716,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.888882582970863</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>10.38885420633975</v>
       </c>
       <c r="D17" t="n">
-        <v>20.30548776693678</v>
+        <v>87.36081946240242</v>
       </c>
     </row>
     <row r="18">
@@ -4730,13 +4730,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>9.63094497866121</v>
+        <v>11.23610247510475</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>64.2062998577414</v>
       </c>
     </row>
     <row r="19">
@@ -4744,13 +4744,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.619924769736241</v>
       </c>
     </row>
     <row r="20">
